--- a/data/trans_orig/P6904-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6904-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2007</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30533</t>
+          <t>31030</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48703</t>
+          <t>48473</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15211</t>
+          <t>14846</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25793</t>
+          <t>25807</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50651</t>
+          <t>50064</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72288</t>
+          <t>71301</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>63,91%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30628</t>
+          <t>30858</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48798</t>
+          <t>48301</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6448</t>
+          <t>6434</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17030</t>
+          <t>17395</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39284</t>
+          <t>40271</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60921</t>
+          <t>61508</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>55,13%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57587</t>
+          <t>57333</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>81850</t>
+          <t>83173</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16098</t>
+          <t>15976</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30261</t>
+          <t>30607</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>78059</t>
+          <t>79227</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>107626</t>
+          <t>107912</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>54,29%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>64131</t>
+          <t>62808</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>88394</t>
+          <t>88648</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22536</t>
+          <t>22190</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36699</t>
+          <t>36821</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>91151</t>
+          <t>90865</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>120718</t>
+          <t>119550</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>60,14%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>51543</t>
+          <t>51100</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>72724</t>
+          <t>72084</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22698</t>
+          <t>23083</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35784</t>
+          <t>35714</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>78238</t>
+          <t>77892</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>103017</t>
+          <t>103689</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>66,26%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37220</t>
+          <t>37860</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58401</t>
+          <t>58844</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10749</t>
+          <t>10819</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23835</t>
+          <t>23450</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>53460</t>
+          <t>52788</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>78239</t>
+          <t>78585</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>50,22%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63408</t>
+          <t>62167</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>87559</t>
+          <t>87359</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31790</t>
+          <t>31692</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51791</t>
+          <t>51011</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>103188</t>
+          <t>100569</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>130465</t>
+          <t>131851</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>58,44%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>49490</t>
+          <t>49690</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>73641</t>
+          <t>74882</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36760</t>
+          <t>37540</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>56761</t>
+          <t>56859</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>95135</t>
+          <t>93749</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>122412</t>
+          <t>125031</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>55,42%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>223693</t>
+          <t>222390</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>268198</t>
+          <t>267606</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>100160</t>
+          <t>98975</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>129872</t>
+          <t>128347</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>333659</t>
+          <t>334291</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>386773</t>
+          <t>387206</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,92%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>204107</t>
+          <t>204699</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>248612</t>
+          <t>249915</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>90249</t>
+          <t>91774</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>119961</t>
+          <t>121146</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>305654</t>
+          <t>305221</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>358768</t>
+          <t>358136</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>51,72%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2012</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2012 (tasa de respuesta: 98,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36403</t>
+          <t>35270</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53038</t>
+          <t>52214</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16188</t>
+          <t>16053</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27390</t>
+          <t>27079</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54644</t>
+          <t>55991</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75575</t>
+          <t>76504</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>68,41%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23542</t>
+          <t>24366</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40177</t>
+          <t>41310</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7864</t>
+          <t>8175</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19066</t>
+          <t>19201</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36259</t>
+          <t>35330</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57190</t>
+          <t>55843</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>49,93%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43136</t>
+          <t>43189</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63288</t>
+          <t>62316</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25412</t>
+          <t>24863</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41805</t>
+          <t>41705</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>75329</t>
+          <t>73001</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>99886</t>
+          <t>98526</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>64,73%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27597</t>
+          <t>28569</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>47749</t>
+          <t>47696</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19526</t>
+          <t>19626</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35919</t>
+          <t>36468</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>52330</t>
+          <t>53690</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>76887</t>
+          <t>79215</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>52,04%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35453</t>
+          <t>35425</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53593</t>
+          <t>53901</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13844</t>
+          <t>13590</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28065</t>
+          <t>27719</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>53780</t>
+          <t>54430</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77777</t>
+          <t>77377</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>58,38%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25964</t>
+          <t>25656</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44104</t>
+          <t>44132</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24914</t>
+          <t>25260</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39135</t>
+          <t>39389</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>54759</t>
+          <t>55159</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>78756</t>
+          <t>78106</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>58,93%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27249</t>
+          <t>27947</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44236</t>
+          <t>44738</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25681</t>
+          <t>25657</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41889</t>
+          <t>42671</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57307</t>
+          <t>57629</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82512</t>
+          <t>82852</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>58,13%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34196</t>
+          <t>33694</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>51183</t>
+          <t>50485</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22207</t>
+          <t>21425</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38415</t>
+          <t>38439</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>60017</t>
+          <t>59677</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>85222</t>
+          <t>84900</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>59,57%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>160143</t>
+          <t>159921</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>197915</t>
+          <t>196372</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>94801</t>
+          <t>96046</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>124703</t>
+          <t>125458</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>264194</t>
+          <t>265561</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>312849</t>
+          <t>316514</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>58,71%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>127540</t>
+          <t>129083</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>165312</t>
+          <t>165534</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>88958</t>
+          <t>88203</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>118860</t>
+          <t>117615</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>226267</t>
+          <t>222602</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>274922</t>
+          <t>273555</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>50,74%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2016</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20135</t>
+          <t>20081</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35981</t>
+          <t>34696</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16096</t>
+          <t>15702</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25438</t>
+          <t>25528</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39932</t>
+          <t>39485</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59788</t>
+          <t>58599</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>69,28%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18692</t>
+          <t>19977</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34538</t>
+          <t>34592</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4477</t>
+          <t>4387</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13819</t>
+          <t>14213</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24800</t>
+          <t>25989</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44656</t>
+          <t>45103</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>53,32%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53190</t>
+          <t>53017</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73118</t>
+          <t>73068</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29753</t>
+          <t>29635</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44169</t>
+          <t>43827</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86690</t>
+          <t>88725</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>112864</t>
+          <t>112923</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>74,03%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23866</t>
+          <t>23916</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>43794</t>
+          <t>43967</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11383</t>
+          <t>11725</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25799</t>
+          <t>25917</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>39671</t>
+          <t>39612</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>65845</t>
+          <t>63810</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>41,83%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53984</t>
+          <t>54216</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74665</t>
+          <t>74604</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38018</t>
+          <t>37835</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52363</t>
+          <t>52285</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>97478</t>
+          <t>96828</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>123395</t>
+          <t>123349</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,61%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35270</t>
+          <t>35331</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55951</t>
+          <t>55719</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12384</t>
+          <t>12462</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26729</t>
+          <t>26912</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>51287</t>
+          <t>51333</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>77204</t>
+          <t>77854</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>44,57%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41871</t>
+          <t>42312</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>61083</t>
+          <t>60792</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31126</t>
+          <t>32447</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47791</t>
+          <t>47892</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>79448</t>
+          <t>80861</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>104736</t>
+          <t>104836</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,86%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27327</t>
+          <t>27618</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>46539</t>
+          <t>46098</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18292</t>
+          <t>18191</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34957</t>
+          <t>33636</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>49757</t>
+          <t>49657</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>75045</t>
+          <t>73632</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>47,66%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>189336</t>
+          <t>189315</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>227259</t>
+          <t>228223</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>131567</t>
+          <t>131790</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>159313</t>
+          <t>158949</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>330461</t>
+          <t>331123</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>377016</t>
+          <t>377794</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,71%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>122742</t>
+          <t>121778</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>160665</t>
+          <t>160686</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>56985</t>
+          <t>57349</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>84731</t>
+          <t>84508</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>189283</t>
+          <t>188505</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>235838</t>
+          <t>235176</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,53%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2023</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>46112</t>
+          <t>45681</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60608</t>
+          <t>60649</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27039</t>
+          <t>26945</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38955</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>77323</t>
+          <t>77144</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95461</t>
+          <t>96181</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>76,4%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10607</t>
+          <t>10566</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25103</t>
+          <t>25534</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15686</t>
+          <t>15726</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27642</t>
+          <t>27736</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30436</t>
+          <t>29716</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48574</t>
+          <t>48753</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,72%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60979</t>
+          <t>60432</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83150</t>
+          <t>81238</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53201</t>
+          <t>53678</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69708</t>
+          <t>68900</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>119010</t>
+          <t>118894</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>147071</t>
+          <t>146319</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,44%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28833</t>
+          <t>30745</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>51004</t>
+          <t>51551</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>29022</t>
+          <t>29830</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>45529</t>
+          <t>45052</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>63641</t>
+          <t>64393</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>91702</t>
+          <t>91818</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,58%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13372</t>
+          <t>13316</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27898</t>
+          <t>28152</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45324</t>
+          <t>46515</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>84671</t>
+          <t>85664</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62491</t>
+          <t>63270</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>120748</t>
+          <t>120638</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,27%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27379</t>
+          <t>27125</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41905</t>
+          <t>41961</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12237</t>
+          <t>11244</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51584</t>
+          <t>50393</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31436</t>
+          <t>31546</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>89693</t>
+          <t>88914</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>58,43%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50029</t>
+          <t>52097</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>71810</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61970</t>
+          <t>61151</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79335</t>
+          <t>78537</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>118964</t>
+          <t>117940</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>146561</t>
+          <t>145136</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>70,82%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>29027</t>
+          <t>29220</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>51001</t>
+          <t>48933</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24561</t>
+          <t>25359</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>41926</t>
+          <t>42745</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>58365</t>
+          <t>59790</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>85962</t>
+          <t>86986</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>42,45%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>188867</t>
+          <t>188962</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>227692</t>
+          <t>227403</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>210530</t>
+          <t>211471</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>266559</t>
+          <t>267993</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>409751</t>
+          <t>410195</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>480048</t>
+          <t>477653</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>68,85%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>111813</t>
+          <t>112102</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>150638</t>
+          <t>150543</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>87656</t>
+          <t>86222</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>143685</t>
+          <t>142744</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>213672</t>
+          <t>216067</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>283969</t>
+          <t>283525</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>40,87%</t>
         </is>
       </c>
     </row>
